--- a/daily_matches/job_matches_2026-07-05.xlsx
+++ b/daily_matches/job_matches_2026-07-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Data Scientist (Transcriptomics &amp; cfRNA for Alzheimer’s Disease Research)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Superfluid DX, Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, XGBoost, EC2, AKS, CI/CD, Git</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,42 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7af6d0b20c0523a8</t>
+          <t>https://www.indeed.com/viewjob?jk=712a5fae027b3df4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sr. Quality Engineer- First Dollar (Remote)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Inspira Financial</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Oak Brook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Jenkins, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ca2d9e081da9853</t>
         </is>
       </c>
     </row>
